--- a/output/laminas_comunales/comunal_s_isapre_a_2024_biobio.xlsx
+++ b/output/laminas_comunales/comunal_s_isapre_a_2024_biobio.xlsx
@@ -375,46 +375,46 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>8101</t>
+          <t>8108</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Concepción</t>
+          <t>San Pedro de la Paz</t>
         </is>
       </c>
       <c r="C2">
-        <v>39563</v>
+        <v>18.6635200952579</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>8108</t>
+          <t>8101</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>San Pedro de la Paz</t>
+          <t>Concepción</t>
         </is>
       </c>
       <c r="C3">
-        <v>26019</v>
+        <v>17.47690758173457</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>8301</t>
+          <t>8103</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Los Angeles</t>
+          <t>Chiguayante</t>
         </is>
       </c>
       <c r="C4">
-        <v>17806</v>
+        <v>14.36542525092446</v>
       </c>
     </row>
     <row r="5">
@@ -429,22 +429,22 @@
         </is>
       </c>
       <c r="C5">
-        <v>14373</v>
+        <v>9.581105763462077</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>8103</t>
+          <t>8301</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Chiguayante</t>
+          <t>Los Angeles</t>
         </is>
       </c>
       <c r="C6">
-        <v>13053</v>
+        <v>7.889792807642545</v>
       </c>
     </row>
     <row r="7">
@@ -459,37 +459,37 @@
         </is>
       </c>
       <c r="C7">
-        <v>7016</v>
+        <v>7.210243972622449</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>8102</t>
+          <t>8304</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Coronel</t>
+          <t>Laja</t>
         </is>
       </c>
       <c r="C8">
-        <v>4665</v>
+        <v>5.801031124689707</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>8111</t>
+          <t>8202</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Tomé</t>
+          <t>Arauco</t>
         </is>
       </c>
       <c r="C9">
-        <v>2836</v>
+        <v>5.518947713903406</v>
       </c>
     </row>
     <row r="10">
@@ -504,127 +504,127 @@
         </is>
       </c>
       <c r="C10">
-        <v>2484</v>
+        <v>4.867724867724868</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>8202</t>
+          <t>8111</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Arauco</t>
+          <t>Tomé</t>
         </is>
       </c>
       <c r="C11">
-        <v>2186</v>
+        <v>4.68690608008726</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>8304</t>
+          <t>8306</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Laja</t>
+          <t>Nacimiento</t>
         </is>
       </c>
       <c r="C12">
-        <v>1519</v>
+        <v>4.412755844063708</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>8303</t>
+          <t>8104</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Cabrero</t>
+          <t>Florida</t>
         </is>
       </c>
       <c r="C13">
-        <v>1261</v>
+        <v>4.381694255111976</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>8306</t>
+          <t>8307</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Nacimiento</t>
+          <t>Negrete</t>
         </is>
       </c>
       <c r="C14">
-        <v>1244</v>
+        <v>3.896976483762598</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>8106</t>
+          <t>8303</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Lota</t>
+          <t>Cabrero</t>
         </is>
       </c>
       <c r="C15">
-        <v>950</v>
+        <v>3.741839762611276</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>8305</t>
+          <t>8102</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Mulchén</t>
+          <t>Coronel</t>
         </is>
       </c>
       <c r="C16">
-        <v>939</v>
+        <v>3.734898281066107</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>8105</t>
+          <t>8310</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Hualqui</t>
+          <t>San Rosendo</t>
         </is>
       </c>
       <c r="C17">
-        <v>907</v>
+        <v>3.672032193158954</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>8203</t>
+          <t>8109</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Cañete</t>
+          <t>Santa Juana</t>
         </is>
       </c>
       <c r="C18">
-        <v>892</v>
+        <v>3.593289503513942</v>
       </c>
     </row>
     <row r="19">
@@ -639,232 +639,232 @@
         </is>
       </c>
       <c r="C19">
-        <v>800</v>
+        <v>3.23637687608722</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>8205</t>
+          <t>8312</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Curanilahue</t>
+          <t>Tucapel</t>
         </is>
       </c>
       <c r="C20">
-        <v>712</v>
+        <v>3.216407037991707</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>8109</t>
+          <t>8105</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Santa Juana</t>
+          <t>Hualqui</t>
         </is>
       </c>
       <c r="C21">
-        <v>634</v>
+        <v>3.187152997399677</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>8104</t>
+          <t>8302</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Florida</t>
+          <t>Antuco</t>
         </is>
       </c>
       <c r="C22">
-        <v>585</v>
+        <v>2.925311203319502</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>8312</t>
+          <t>8305</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Tucapel</t>
+          <t>Mulchén</t>
         </is>
       </c>
       <c r="C23">
-        <v>574</v>
+        <v>2.864551555826724</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>8201</t>
+          <t>8311</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Lebu</t>
+          <t>Santa Bárbara</t>
         </is>
       </c>
       <c r="C24">
-        <v>529</v>
+        <v>2.410383189122373</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>8307</t>
+          <t>8203</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Negrete</t>
+          <t>Cañete</t>
         </is>
       </c>
       <c r="C25">
-        <v>522</v>
+        <v>2.361662695260789</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>8206</t>
+          <t>8204</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Los Alamos</t>
+          <t>Contulmo</t>
         </is>
       </c>
       <c r="C26">
-        <v>434</v>
+        <v>2.218191964285714</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>8311</t>
+          <t>8314</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Santa Bárbara</t>
+          <t>Alto Biobío</t>
         </is>
       </c>
       <c r="C27">
-        <v>390</v>
+        <v>2.030075187969925</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>8309</t>
+          <t>8106</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Quilleco</t>
+          <t>Lota</t>
         </is>
       </c>
       <c r="C28">
-        <v>189</v>
+        <v>2.018742429715889</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>8314</t>
+          <t>8205</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Alto Biobío</t>
+          <t>Curanilahue</t>
         </is>
       </c>
       <c r="C29">
-        <v>162</v>
+        <v>1.988104878116885</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>8204</t>
+          <t>8201</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Contulmo</t>
+          <t>Lebu</t>
         </is>
       </c>
       <c r="C30">
-        <v>159</v>
+        <v>1.948004124318751</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>8310</t>
+          <t>8308</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>San Rosendo</t>
+          <t>Quilaco</t>
         </is>
       </c>
       <c r="C31">
-        <v>146</v>
+        <v>1.945447252306458</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>8302</t>
+          <t>8309</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Antuco</t>
+          <t>Quilleco</t>
         </is>
       </c>
       <c r="C32">
-        <v>141</v>
+        <v>1.789942229377782</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>8207</t>
+          <t>8206</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Tirúa</t>
+          <t>Los Alamos</t>
         </is>
       </c>
       <c r="C33">
-        <v>135</v>
+        <v>1.69458435828355</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>8308</t>
+          <t>8207</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Quilaco</t>
+          <t>Tirúa</t>
         </is>
       </c>
       <c r="C34">
-        <v>97</v>
+        <v>1.153451811346548</v>
       </c>
     </row>
   </sheetData>
@@ -920,7 +920,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Personas afiliadas a ISAPRE</t>
+          <t>Porcentaje de residentes afiliados a ISAPRE</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
